--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["carousel-hero","cards-business","cards-purpose","cards-performance","cards-performance","cards-future","cards-news","cards-work","accordion-faq"]</t>
+    <t>["carousel-hero","cards-business","cards-purpose","cards-performance","cards-future","cards-news","cards-work","accordion-faq"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-21T08:24:23.579Z</t>
+    <t>2026-04-21T09:33:21.904Z</t>
   </si>
   <si>
     <t>The Mahindra Group Official Website | Together We Rise</t>
